--- a/vendor-report/1 X CATERPILLAR 6060 IN CKD FORM - LOAD 10-16 - VARIOUS - 6 X LINKS - 2604DSI2804- BA3188 -DURBAN PORT TO KAMOTO COPPER COMPANY.xlsx
+++ b/vendor-report/1 X CATERPILLAR 6060 IN CKD FORM - LOAD 10-16 - VARIOUS - 6 X LINKS - 2604DSI2804- BA3188 -DURBAN PORT TO KAMOTO COPPER COMPANY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mercy FFW\Desktop\PROJECTS\GIFT - IMPORTS\GIFT - IMPORTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A1532F0-27A8-4B6A-A82C-75ECAF03894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9930462B-9126-4EA1-94C6-027EE507BDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4680" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROJECT CARGO" sheetId="47" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>LOADING POINT</t>
   </si>
@@ -210,7 +210,25 @@
     <t>DENGU, WILFANOS</t>
   </si>
   <si>
-    <t xml:space="preserve">IN QUEUE EXITING WHISKEY PARKING </t>
+    <t>LUKUNI LUBUMBASHI</t>
+  </si>
+  <si>
+    <t>KOLWEZI KCC</t>
+  </si>
+  <si>
+    <t>WAITING TO OFFLOAD</t>
+  </si>
+  <si>
+    <t>LIKASI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN TRANSIT </t>
+  </si>
+  <si>
+    <t>LUMATA</t>
+  </si>
+  <si>
+    <t>TENKE FUNGURUME</t>
   </si>
 </sst>
 </file>
@@ -500,26 +518,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -536,9 +551,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -551,12 +563,6 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -566,14 +572,26 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -583,7 +601,47 @@
     <cellStyle name="Normal 28" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -650,46 +708,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -743,6 +761,36 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D9D9"/>
           <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1199,13 +1247,13 @@
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="6"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
@@ -1251,110 +1299,110 @@
       <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:24" s="1" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="23"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="22"/>
     </row>
     <row r="7" spans="1:24" s="1" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="34" t="s">
+      <c r="J7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="25" t="s">
+      <c r="N7" s="16"/>
+      <c r="O7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="25" t="s">
+      <c r="P7" s="24"/>
+      <c r="Q7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="26"/>
-      <c r="S7" s="25" t="s">
+      <c r="R7" s="24"/>
+      <c r="S7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="T7" s="26"/>
-      <c r="U7" s="27" t="s">
+      <c r="T7" s="24"/>
+      <c r="U7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="V7" s="28"/>
-      <c r="W7" s="35" t="s">
+      <c r="V7" s="26"/>
+      <c r="W7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="X7" s="24" t="s">
+      <c r="X7" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:24" s="1" customFormat="1">
-      <c r="A8" s="30"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
       <c r="M8" s="10" t="s">
         <v>20</v>
       </c>
@@ -1385,428 +1433,429 @@
       <c r="V8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="W8" s="24"/>
-      <c r="X8" s="36"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="17"/>
     </row>
-    <row r="9" spans="1:24" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A9" s="12">
+    <row r="9" spans="1:24" s="30" customFormat="1">
+      <c r="A9" s="30">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="31">
+        <v>46174</v>
+      </c>
+      <c r="J9" s="32">
+        <v>46172</v>
+      </c>
+      <c r="K9" s="32">
+        <v>46174</v>
+      </c>
+      <c r="L9" s="32">
+        <v>46175</v>
+      </c>
+      <c r="M9" s="32">
+        <v>46177</v>
+      </c>
+      <c r="N9" s="32">
+        <v>46180</v>
+      </c>
+      <c r="O9" s="32">
+        <v>46182</v>
+      </c>
+      <c r="P9" s="32">
+        <v>46184</v>
+      </c>
+      <c r="Q9" s="32">
+        <v>46186</v>
+      </c>
+      <c r="R9" s="32">
+        <v>46187</v>
+      </c>
+      <c r="S9" s="32">
+        <v>46187</v>
+      </c>
+      <c r="T9" s="32">
+        <v>46190</v>
+      </c>
+      <c r="U9" s="32">
+        <v>46193</v>
+      </c>
+      <c r="W9" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="X9" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" s="30" customFormat="1" ht="18" customHeight="1">
+      <c r="A10" s="30">
+        <v>2</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="31">
+        <v>46174</v>
+      </c>
+      <c r="J10" s="32">
+        <v>46172</v>
+      </c>
+      <c r="K10" s="32">
+        <v>46174</v>
+      </c>
+      <c r="L10" s="32">
+        <v>46175</v>
+      </c>
+      <c r="M10" s="32">
+        <v>46177</v>
+      </c>
+      <c r="N10" s="32">
+        <v>46179</v>
+      </c>
+      <c r="O10" s="32">
+        <v>46182</v>
+      </c>
+      <c r="P10" s="32">
+        <v>46184</v>
+      </c>
+      <c r="Q10" s="32">
+        <v>46186</v>
+      </c>
+      <c r="R10" s="32">
+        <v>46187</v>
+      </c>
+      <c r="S10" s="32">
+        <v>46187</v>
+      </c>
+      <c r="T10" s="32">
+        <v>46190</v>
+      </c>
+      <c r="U10" s="32">
+        <v>46193</v>
+      </c>
+      <c r="W10" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="X10" s="30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" s="30" customFormat="1">
+      <c r="A11" s="30">
+        <v>3</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="31">
+        <v>46174</v>
+      </c>
+      <c r="J11" s="32">
+        <v>46172</v>
+      </c>
+      <c r="K11" s="32">
+        <v>46174</v>
+      </c>
+      <c r="L11" s="32">
+        <v>46175</v>
+      </c>
+      <c r="M11" s="32">
+        <v>46177</v>
+      </c>
+      <c r="N11" s="32">
+        <v>46179</v>
+      </c>
+      <c r="O11" s="32">
+        <v>46182</v>
+      </c>
+      <c r="P11" s="32">
+        <v>46184</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>46186</v>
+      </c>
+      <c r="R11" s="32">
+        <v>46187</v>
+      </c>
+      <c r="S11" s="32">
+        <v>46187</v>
+      </c>
+      <c r="T11" s="32">
+        <v>46190</v>
+      </c>
+      <c r="W11" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="X11" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A12" s="30">
+        <v>5</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E12" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F12" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G12" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I12" s="35">
         <v>46174</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J12" s="32">
         <v>46172</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K12" s="32">
         <v>46174</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L12" s="32">
         <v>46175</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M12" s="32">
         <v>46178</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N12" s="32">
         <v>46179</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O12" s="32">
         <v>46181</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P12" s="32">
         <v>46183</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q12" s="32">
         <v>46185</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R12" s="32">
         <v>46187</v>
       </c>
-      <c r="S9" s="16">
+      <c r="S12" s="32">
         <v>46187</v>
       </c>
-      <c r="T9" s="16">
+      <c r="T12" s="32">
         <v>46190</v>
       </c>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X9" s="12" t="s">
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="30" t="s">
         <v>58</v>
       </c>
+      <c r="X12" s="30" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="10" spans="1:24" s="12" customFormat="1">
-      <c r="A10" s="12">
-        <v>2</v>
-      </c>
-      <c r="B10" s="12" t="s">
+    <row r="13" spans="1:24" s="30" customFormat="1">
+      <c r="A13" s="30">
+        <v>4</v>
+      </c>
+      <c r="B13" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C13" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="D13" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="31">
         <v>46174</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J13" s="32">
         <v>46172</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K13" s="32">
         <v>46174</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L13" s="32">
         <v>46175</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M13" s="32">
         <v>46177</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N13" s="32">
+        <v>46179</v>
+      </c>
+      <c r="O13" s="32">
+        <v>46182</v>
+      </c>
+      <c r="P13" s="32">
+        <v>46184</v>
+      </c>
+      <c r="Q13" s="32">
+        <v>46186</v>
+      </c>
+      <c r="R13" s="32">
+        <v>46187</v>
+      </c>
+      <c r="S13" s="32">
+        <v>46187</v>
+      </c>
+      <c r="T13" s="32">
+        <v>46190</v>
+      </c>
+      <c r="W13" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="X13" s="30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" s="30" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A14" s="30">
+        <v>6</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="31">
+        <v>46174</v>
+      </c>
+      <c r="J14" s="32">
+        <v>46172</v>
+      </c>
+      <c r="K14" s="32">
+        <v>46173</v>
+      </c>
+      <c r="L14" s="32">
+        <v>46174</v>
+      </c>
+      <c r="M14" s="32">
+        <v>46178</v>
+      </c>
+      <c r="N14" s="32">
         <v>46180</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O14" s="32">
         <v>46182</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P14" s="32">
         <v>46184</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q14" s="32">
         <v>46186</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R14" s="32">
         <v>46187</v>
       </c>
-      <c r="S10" s="16">
+      <c r="S14" s="32">
         <v>46187</v>
       </c>
-      <c r="T10" s="16">
+      <c r="T14" s="32">
         <v>46190</v>
       </c>
-      <c r="W10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X10" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" s="12" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="12">
-        <v>3</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="17">
-        <v>46174</v>
-      </c>
-      <c r="J11" s="16">
-        <v>46172</v>
-      </c>
-      <c r="K11" s="16">
-        <v>46174</v>
-      </c>
-      <c r="L11" s="16">
-        <v>46175</v>
-      </c>
-      <c r="M11" s="16">
-        <v>46177</v>
-      </c>
-      <c r="N11" s="16">
-        <v>46179</v>
-      </c>
-      <c r="O11" s="16">
-        <v>46182</v>
-      </c>
-      <c r="P11" s="16">
-        <v>46184</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>46186</v>
-      </c>
-      <c r="R11" s="16">
-        <v>46187</v>
-      </c>
-      <c r="S11" s="16">
-        <v>46187</v>
-      </c>
-      <c r="T11" s="16">
-        <v>46190</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X11" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" s="12" customFormat="1">
-      <c r="A12" s="12">
-        <v>4</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="17">
-        <v>46174</v>
-      </c>
-      <c r="J12" s="16">
-        <v>46172</v>
-      </c>
-      <c r="K12" s="16">
-        <v>46174</v>
-      </c>
-      <c r="L12" s="16">
-        <v>46175</v>
-      </c>
-      <c r="M12" s="16">
-        <v>46177</v>
-      </c>
-      <c r="N12" s="16">
-        <v>46179</v>
-      </c>
-      <c r="O12" s="16">
-        <v>46182</v>
-      </c>
-      <c r="P12" s="16">
-        <v>46184</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>46186</v>
-      </c>
-      <c r="R12" s="16">
-        <v>46187</v>
-      </c>
-      <c r="S12" s="16">
-        <v>46187</v>
-      </c>
-      <c r="T12" s="16">
-        <v>46190</v>
-      </c>
-      <c r="W12" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X12" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" s="12" customFormat="1">
-      <c r="A13" s="12">
-        <v>5</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="17">
-        <v>46174</v>
-      </c>
-      <c r="J13" s="16">
-        <v>46172</v>
-      </c>
-      <c r="K13" s="16">
-        <v>46174</v>
-      </c>
-      <c r="L13" s="16">
-        <v>46175</v>
-      </c>
-      <c r="M13" s="16">
-        <v>46177</v>
-      </c>
-      <c r="N13" s="16">
-        <v>46179</v>
-      </c>
-      <c r="O13" s="16">
-        <v>46182</v>
-      </c>
-      <c r="P13" s="16">
-        <v>46184</v>
-      </c>
-      <c r="Q13" s="16">
-        <v>46186</v>
-      </c>
-      <c r="R13" s="16">
-        <v>46187</v>
-      </c>
-      <c r="S13" s="16">
-        <v>46187</v>
-      </c>
-      <c r="T13" s="16">
-        <v>46190</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X13" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" s="12" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A14" s="12">
-        <v>6</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="17">
-        <v>46174</v>
-      </c>
-      <c r="J14" s="16">
-        <v>46172</v>
-      </c>
-      <c r="K14" s="16">
-        <v>46173</v>
-      </c>
-      <c r="L14" s="16">
-        <v>46174</v>
-      </c>
-      <c r="M14" s="16">
-        <v>46178</v>
-      </c>
-      <c r="N14" s="16">
-        <v>46180</v>
-      </c>
-      <c r="O14" s="16">
-        <v>46182</v>
-      </c>
-      <c r="P14" s="16">
-        <v>46184</v>
-      </c>
-      <c r="Q14" s="16">
-        <v>46186</v>
-      </c>
-      <c r="R14" s="16">
-        <v>46187</v>
-      </c>
-      <c r="S14" s="16">
-        <v>46187</v>
-      </c>
-      <c r="T14" s="16">
-        <v>46190</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X14" s="12" t="s">
-        <v>58</v>
+      <c r="W14" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="X14" s="30" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:24" s="11" customFormat="1"/>
   </sheetData>
   <autoFilter ref="A8:X8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="21">
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A6:X6"/>
     <mergeCell ref="M7:N7"/>
@@ -1823,44 +1872,52 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="X7:X8"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="15" priority="33">
+    <cfRule type="expression" dxfId="15" priority="39">
       <formula>$AB14 = "Completed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:D1048576 D1:D8 D10:D13">
-    <cfRule type="duplicateValues" dxfId="14" priority="148"/>
+  <conditionalFormatting sqref="D15:D1048576 D1:D11 D13">
+    <cfRule type="duplicateValues" dxfId="14" priority="179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:D1048576">
+    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="10" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:D1048576 D1:D13">
-    <cfRule type="duplicateValues" dxfId="13" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="132"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="96"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9">
-    <cfRule type="duplicateValues" dxfId="6" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="207"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
